--- a/data/processed/indicadores_ENV_SIEPAC.xlsx
+++ b/data/processed/indicadores_ENV_SIEPAC.xlsx
@@ -1865,10 +1865,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2047,7 +2047,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Promedio regional</t>
+          <t>Promedio de países (media simple)</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
@@ -2064,6 +2064,28 @@
       </c>
       <c r="F10" s="9" t="n">
         <v>0.2500564377547951</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agregado regional (razón de sumas)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>0.166086</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.174519</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.134331</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.211507</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.238027</v>
       </c>
     </row>
   </sheetData>
@@ -2077,10 +2099,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2259,7 +2281,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Promedio regional</t>
+          <t>Promedio de países (media simple)</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
@@ -2276,6 +2298,28 @@
       </c>
       <c r="F10" s="9" t="n">
         <v>0.05348193946297091</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agregado regional (razón de sumas)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>0.03257</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.031233</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.022967</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.034969</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.038537</v>
       </c>
     </row>
   </sheetData>
@@ -2289,10 +2333,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2471,7 +2515,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Promedio regional</t>
+          <t>Promedio de países (media simple)</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
@@ -2488,6 +2532,28 @@
       </c>
       <c r="F10" s="11" t="n">
         <v>1.619492523980882</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agregado regional (razón de sumas)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>1.446198</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>1.445258</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1.162884</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1.669315</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>1.799328</v>
       </c>
     </row>
   </sheetData>
@@ -2501,10 +2567,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2683,7 +2749,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Promedio regional</t>
+          <t>Promedio de países (media simple)</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
@@ -2700,6 +2766,28 @@
       </c>
       <c r="F10" s="9" t="n">
         <v>0.06123078861414056</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agregado regional (razón de sumas)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>0.042665</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.037793</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.041677</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.058023</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.05791</v>
       </c>
     </row>
   </sheetData>
@@ -2713,10 +2801,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -2895,7 +2983,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Promedio regional</t>
+          <t>Promedio de países (media simple)</t>
         </is>
       </c>
       <c r="B10" s="9" t="n">
@@ -2912,6 +3000,28 @@
       </c>
       <c r="F10" s="9" t="n">
         <v>0.4474515183775523</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agregado regional (razón de sumas)</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>0.283603</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>0.258651</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.198823</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.275991</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.291314</v>
       </c>
     </row>
   </sheetData>
@@ -2925,10 +3035,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -3107,7 +3217,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Promedio regional</t>
+          <t>Promedio de países (media simple)</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
@@ -3124,6 +3234,28 @@
       </c>
       <c r="F10" s="13" t="n">
         <v>0.01763966964207691</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agregado regional (razón de sumas)</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>0.008366999999999999</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0.006764</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0.007126</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>0.009593000000000001</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.009376000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3137,10 +3269,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
@@ -3319,7 +3451,7 @@
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Promedio regional</t>
+          <t>Promedio de países (media simple)</t>
         </is>
       </c>
       <c r="B10" s="11" t="n">
@@ -3336,6 +3468,28 @@
       </c>
       <c r="F10" s="11" t="n">
         <v>1.823140915542606</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agregado regional (razón de sumas)</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
+        <v>1.490715</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>1.381786</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1.157869</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1.626593</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>1.727963</v>
       </c>
     </row>
   </sheetData>
